--- a/diseases/d030/2010-2014.xlsx
+++ b/diseases/d030/2010-2014.xlsx
@@ -769,11 +769,11 @@
         <v>8</v>
       </c>
       <c r="R2" t="n">
-        <v>0.006584975902177102</v>
+        <v>0.006637283635739908</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -917,11 +917,11 @@
         <v>12</v>
       </c>
       <c r="R3" t="n">
-        <v>0.005993067955913992</v>
+        <v>0.006040673870729579</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1065,11 +1065,11 @@
         <v>11</v>
       </c>
       <c r="R4" t="n">
-        <v>0.007842780287986212</v>
+        <v>0.007905079386386855</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -1213,11 +1213,11 @@
         <v>6</v>
       </c>
       <c r="R5" t="n">
-        <v>0.006289021929045548</v>
+        <v>0.006338978753234743</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -1361,11 +1361,11 @@
         <v>2</v>
       </c>
       <c r="R6" t="n">
-        <v>0.004957229049953549</v>
+        <v>0.004996606781961504</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -1509,11 +1509,11 @@
         <v>6</v>
       </c>
       <c r="R7" t="n">
-        <v>0.007694803301420434</v>
+        <v>0.007755926945134274</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -1657,11 +1657,11 @@
         <v>7</v>
       </c>
       <c r="R8" t="n">
-        <v>0.007028906861874434</v>
+        <v>0.007084740959497655</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -1805,11 +1805,11 @@
         <v>10</v>
       </c>
       <c r="R9" t="n">
-        <v>0.007842780287986212</v>
+        <v>0.007905079386386855</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -1953,11 +1953,11 @@
         <v>10</v>
       </c>
       <c r="R10" t="n">
-        <v>0.008878619193946655</v>
+        <v>0.008949146475154933</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -2101,11 +2101,11 @@
         <v>10</v>
       </c>
       <c r="R11" t="n">
-        <v>0.008878619193946655</v>
+        <v>0.008949146475154933</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -2249,11 +2249,11 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.007694803301420434</v>
+        <v>0.007755926945134274</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -2397,11 +2397,11 @@
         <v>8</v>
       </c>
       <c r="R13" t="n">
-        <v>0.00673295288874288</v>
+        <v>0.00678643607699249</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -2545,11 +2545,11 @@
         <v>9</v>
       </c>
       <c r="R14" t="n">
-        <v>0.00602830067575387</v>
+        <v>0.006077855851048059</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -2693,11 +2693,11 @@
         <v>5</v>
       </c>
       <c r="R15" t="n">
-        <v>0.004190404128267934</v>
+        <v>0.004224851018411456</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -2841,11 +2841,11 @@
         <v>4</v>
       </c>
       <c r="R16" t="n">
-        <v>0.004190404128267934</v>
+        <v>0.004224851018411456</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -2989,11 +2989,11 @@
         <v>8</v>
       </c>
       <c r="R17" t="n">
-        <v>0.004263919990167371</v>
+        <v>0.00429897121171692</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -3137,11 +3137,11 @@
         <v>3</v>
       </c>
       <c r="R18" t="n">
-        <v>0.005219626194860058</v>
+        <v>0.005262533724687954</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -3285,11 +3285,11 @@
         <v>6</v>
       </c>
       <c r="R19" t="n">
-        <v>0.00485204688536287</v>
+        <v>0.004891932758160633</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -3433,11 +3433,11 @@
         <v>4</v>
       </c>
       <c r="R20" t="n">
-        <v>0.005513689642457808</v>
+        <v>0.005559014497909811</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -3581,11 +3581,11 @@
         <v>5</v>
       </c>
       <c r="R21" t="n">
-        <v>0.006395879985251057</v>
+        <v>0.00644845681757538</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -3729,11 +3729,11 @@
         <v>4</v>
       </c>
       <c r="R22" t="n">
-        <v>0.004778531023463433</v>
+        <v>0.004817812564855169</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -3877,11 +3877,11 @@
         <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>0.006763459294748243</v>
+        <v>0.006819057784102701</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -4025,11 +4025,11 @@
         <v>6</v>
       </c>
       <c r="R24" t="n">
-        <v>0.005587205504357245</v>
+        <v>0.005633134691215275</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -4173,11 +4173,11 @@
         <v>4</v>
       </c>
       <c r="R25" t="n">
-        <v>0.00485204688536287</v>
+        <v>0.004891932758160633</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
@@ -4321,11 +4321,11 @@
         <v>8</v>
       </c>
       <c r="R26" t="n">
-        <v>0.004527130736532127</v>
+        <v>0.004561439649210577</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
@@ -4469,11 +4469,11 @@
         <v>2</v>
       </c>
       <c r="R27" t="n">
-        <v>0.003650911884300102</v>
+        <v>0.003678580362266594</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
@@ -4617,11 +4617,11 @@
         <v>8</v>
       </c>
       <c r="R28" t="n">
-        <v>0.004527130736532127</v>
+        <v>0.004561439649210577</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -4765,11 +4765,11 @@
         <v>4</v>
       </c>
       <c r="R29" t="n">
-        <v>0.0035778936466141</v>
+        <v>0.003605008755021262</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
@@ -4913,11 +4913,11 @@
         <v>4</v>
       </c>
       <c r="R30" t="n">
-        <v>0.004308076023474121</v>
+        <v>0.004340724827474581</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
@@ -5061,11 +5061,11 @@
         <v>5</v>
       </c>
       <c r="R31" t="n">
-        <v>0.004235057785788118</v>
+        <v>0.00426715322022925</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
@@ -5209,11 +5209,11 @@
         <v>4</v>
       </c>
       <c r="R32" t="n">
-        <v>0.004673167211904131</v>
+        <v>0.004708582863701241</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
@@ -5357,11 +5357,11 @@
         <v>6</v>
       </c>
       <c r="R33" t="n">
-        <v>0.004673167211904131</v>
+        <v>0.004708582863701241</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
@@ -5505,11 +5505,11 @@
         <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>0.004527130736532127</v>
+        <v>0.004561439649210577</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
@@ -5653,11 +5653,11 @@
         <v>6</v>
       </c>
       <c r="R35" t="n">
-        <v>0.00533033135107815</v>
+        <v>0.005370727328909228</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
@@ -5801,11 +5801,11 @@
         <v>6</v>
       </c>
       <c r="R36" t="n">
-        <v>0.004016003072730112</v>
+        <v>0.004046438398493253</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
@@ -5949,11 +5949,11 @@
         <v>3</v>
       </c>
       <c r="R37" t="n">
-        <v>0.003504875408928099</v>
+        <v>0.00353143714777593</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
@@ -6097,11 +6097,11 @@
         <v>8</v>
       </c>
       <c r="R38" t="n">
-        <v>0.004133405921210798</v>
+        <v>0.004168921785176191</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
@@ -6245,11 +6245,11 @@
         <v>2</v>
       </c>
       <c r="R39" t="n">
-        <v>0.002828119840828441</v>
+        <v>0.002852420168804763</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
@@ -6393,11 +6393,11 @@
         <v>2</v>
       </c>
       <c r="R40" t="n">
-        <v>0.002828119840828441</v>
+        <v>0.002852420168804763</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
@@ -6541,11 +6541,11 @@
         <v>3</v>
       </c>
       <c r="R41" t="n">
-        <v>0.003263215200955893</v>
+        <v>0.003291254040928572</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
@@ -6689,11 +6689,11 @@
         <v>7</v>
       </c>
       <c r="R42" t="n">
-        <v>0.002828119840828441</v>
+        <v>0.002852420168804763</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
@@ -6837,11 +6837,11 @@
         <v>5</v>
       </c>
       <c r="R43" t="n">
-        <v>0.003190699307601318</v>
+        <v>0.003218115062241271</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
@@ -6985,11 +6985,11 @@
         <v>6</v>
       </c>
       <c r="R44" t="n">
-        <v>0.003408246987665044</v>
+        <v>0.003437531998303176</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
@@ -7133,11 +7133,11 @@
         <v>7</v>
       </c>
       <c r="R45" t="n">
-        <v>0.003770826454437921</v>
+        <v>0.003803226891739684</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
@@ -7281,11 +7281,11 @@
         <v>6</v>
       </c>
       <c r="R46" t="n">
-        <v>0.003408246987665044</v>
+        <v>0.003437531998303176</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
@@ -7429,11 +7429,11 @@
         <v>5</v>
       </c>
       <c r="R47" t="n">
-        <v>0.00348076288101962</v>
+        <v>0.003510670976990478</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
@@ -7577,11 +7577,11 @@
         <v>1</v>
       </c>
       <c r="R48" t="n">
-        <v>0.002755603947473866</v>
+        <v>0.002779281190117461</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
@@ -7725,11 +7725,11 @@
         <v>3</v>
       </c>
       <c r="R49" t="n">
-        <v>0.002320508587346413</v>
+        <v>0.002340447317993652</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
@@ -7873,11 +7873,11 @@
         <v>1</v>
       </c>
       <c r="R50" t="n">
-        <v>0.002737846897197967</v>
+        <v>0.002760704996876044</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
@@ -8021,11 +8021,11 @@
         <v>1</v>
       </c>
       <c r="R51" t="n">
-        <v>0.001873263666503872</v>
+        <v>0.001888903418915188</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
@@ -8169,11 +8169,11 @@
         <v>1</v>
       </c>
       <c r="R52" t="n">
-        <v>0.002521701089524443</v>
+        <v>0.00254275460238583</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>nbs_computed</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
@@ -8317,11 +8317,11 @@
         <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>0.0004997872730440379</v>
+        <v>0.0004931730985003484</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
@@ -8417,12 +8417,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>BR-AC</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Acre, Brazil</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -8456,20 +8456,17 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>36</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>0.002593749692082285</v>
+        <v>0</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
@@ -8498,17 +8495,12 @@
       </c>
       <c r="AV54" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
-        </is>
-      </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>All Sources</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -8518,22 +8510,18 @@
       </c>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
-        </is>
-      </c>
-      <c r="BB54" t="inlineStr">
-        <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
-        </is>
-      </c>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB54" t="inlineStr"/>
       <c r="BC54" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -8565,12 +8553,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>BR-AL</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Alagoas, Brazil</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -8595,29 +8583,26 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>2014-05-01</t>
+          <t>2014-04-01</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2014-05</t>
+          <t>2014-04</t>
         </is>
       </c>
       <c r="N55" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>27</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>0.001945312269061713</v>
+        <v>0</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
@@ -8646,17 +8631,12 @@
       </c>
       <c r="AV55" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
-        </is>
-      </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>All Sources</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -8666,22 +8646,18 @@
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
-        </is>
-      </c>
-      <c r="BB55" t="inlineStr">
-        <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
-        </is>
-      </c>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB55" t="inlineStr"/>
       <c r="BC55" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -8713,12 +8689,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>BR-AM</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Amazonas, Brazil</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -8743,29 +8719,26 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>2014-06-01</t>
+          <t>2014-04-01</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2014-06</t>
+          <t>2014-04</t>
         </is>
       </c>
       <c r="N56" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>28</v>
-      </c>
-      <c r="Q56" t="n">
         <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>0.002017360871619555</v>
+        <v>0</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
@@ -8794,17 +8767,12 @@
       </c>
       <c r="AV56" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
-        </is>
-      </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>All Sources</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -8814,22 +8782,18 @@
       </c>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
-        </is>
-      </c>
-      <c r="BB56" t="inlineStr">
-        <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
-        </is>
-      </c>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB56" t="inlineStr"/>
       <c r="BC56" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -8861,12 +8825,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>BR-AP</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Amapá, Brazil</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -8891,29 +8855,26 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>2014-07-01</t>
+          <t>2014-04-01</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2014-07</t>
+          <t>2014-04</t>
         </is>
       </c>
       <c r="N57" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
-        <v>51</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>0.003674478730449904</v>
+        <v>0</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
@@ -8942,17 +8903,12 @@
       </c>
       <c r="AV57" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
-        </is>
-      </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>All Sources</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -8962,22 +8918,18 @@
       </c>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
-        </is>
-      </c>
-      <c r="BB57" t="inlineStr">
-        <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
-        </is>
-      </c>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB57" t="inlineStr"/>
       <c r="BC57" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -9009,12 +8961,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>BR-BA</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Bahia, Brazil</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -9039,29 +8991,26 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>2014-08-01</t>
+          <t>2014-04-01</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>2014-08</t>
+          <t>2014-04</t>
         </is>
       </c>
       <c r="N58" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>32</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>0.00230555528185092</v>
+        <v>0</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
@@ -9090,17 +9039,12 @@
       </c>
       <c r="AV58" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
-        </is>
-      </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>All Sources</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -9110,22 +9054,18 @@
       </c>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
-        </is>
-      </c>
-      <c r="BB58" t="inlineStr">
-        <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
-        </is>
-      </c>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB58" t="inlineStr"/>
       <c r="BC58" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -9157,12 +9097,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>BR-CE</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Ceará, Brazil</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -9187,29 +9127,26 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>2014-09-01</t>
+          <t>2014-04-01</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>2014-09</t>
+          <t>2014-04</t>
         </is>
       </c>
       <c r="N59" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
-        <v>58</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>0.004178818948354792</v>
+        <v>0</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
@@ -9238,17 +9175,12 @@
       </c>
       <c r="AV59" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
-        </is>
-      </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>All Sources</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -9258,22 +9190,18 @@
       </c>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
-        </is>
-      </c>
-      <c r="BB59" t="inlineStr">
-        <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
-        </is>
-      </c>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB59" t="inlineStr"/>
       <c r="BC59" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -9305,12 +9233,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>BR-DF</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Distrito Federal, Brazil</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -9335,29 +9263,26 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>2014-10-01</t>
+          <t>2014-04-01</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>2014-10</t>
+          <t>2014-04</t>
         </is>
       </c>
       <c r="N60" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
-        <v>42</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>0.003026041307429332</v>
+        <v>0</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
@@ -9386,17 +9311,12 @@
       </c>
       <c r="AV60" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
-        </is>
-      </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>All Sources</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -9406,22 +9326,18 @@
       </c>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
-        </is>
-      </c>
-      <c r="BB60" t="inlineStr">
-        <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
-        </is>
-      </c>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB60" t="inlineStr"/>
       <c r="BC60" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -9453,12 +9369,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>BR-ES</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Espírito Santo, Brazil</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -9483,29 +9399,26 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>2014-11-01</t>
+          <t>2014-04-01</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>2014-11</t>
+          <t>2014-04</t>
         </is>
       </c>
       <c r="N61" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
-        <v>32</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>0.00230555528185092</v>
+        <v>0</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
@@ -9534,17 +9447,12 @@
       </c>
       <c r="AV61" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
-        </is>
-      </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>All Sources</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -9554,22 +9462,18 @@
       </c>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
-        </is>
-      </c>
-      <c r="BB61" t="inlineStr">
-        <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
-        </is>
-      </c>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB61" t="inlineStr"/>
       <c r="BC61" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -9601,12 +9505,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>BR-GO</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Goiás, Brazil</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -9631,29 +9535,26 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>2014-12-01</t>
+          <t>2014-04-01</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>2014-12</t>
+          <t>2014-04</t>
         </is>
       </c>
       <c r="N62" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
-        <v>34</v>
-      </c>
-      <c r="Q62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>0.002449652486966602</v>
+        <v>0</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
@@ -9682,40 +9583,3811 @@
       </c>
       <c r="AV62" t="inlineStr">
         <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA62" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB62" t="inlineStr"/>
+      <c r="BC62" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>D030</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>neonatal-tetanus</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Neonatal Tetanus</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>BR-MA</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Maranhão, Brazil</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>D030</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Neonatal Tetanus</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>新生儿破伤风</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>2014-04-01</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>2014-04</t>
+        </is>
+      </c>
+      <c r="N63" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0</v>
+      </c>
+      <c r="R63" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP63" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR63" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS63" t="inlineStr"/>
+      <c r="AT63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV63" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA63" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB63" t="inlineStr"/>
+      <c r="BC63" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>D030</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>neonatal-tetanus</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Neonatal Tetanus</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>BR-MG</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Minas Gerais, Brazil</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>D030</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Neonatal Tetanus</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>新生儿破伤风</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>2014-04-01</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>2014-04</t>
+        </is>
+      </c>
+      <c r="N64" t="n">
+        <v>1</v>
+      </c>
+      <c r="O64" t="n">
+        <v>1</v>
+      </c>
+      <c r="R64" t="n">
+        <v>0.004822973481796675</v>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP64" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR64" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS64" t="inlineStr"/>
+      <c r="AT64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV64" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA64" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB64" t="inlineStr"/>
+      <c r="BC64" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>D030</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>neonatal-tetanus</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Neonatal Tetanus</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>BR-MS</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Mato Grosso do Sul, Brazil</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>D030</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Neonatal Tetanus</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>新生儿破伤风</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>2014-04-01</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>2014-04</t>
+        </is>
+      </c>
+      <c r="N65" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0</v>
+      </c>
+      <c r="R65" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP65" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR65" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS65" t="inlineStr"/>
+      <c r="AT65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV65" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA65" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB65" t="inlineStr"/>
+      <c r="BC65" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>D030</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>neonatal-tetanus</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Neonatal Tetanus</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>BR-MT</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Mato Grosso, Brazil</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>D030</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Neonatal Tetanus</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>新生儿破伤风</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>2014-04-01</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>2014-04</t>
+        </is>
+      </c>
+      <c r="N66" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0</v>
+      </c>
+      <c r="R66" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP66" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR66" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS66" t="inlineStr"/>
+      <c r="AT66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV66" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA66" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB66" t="inlineStr"/>
+      <c r="BC66" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>D030</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>neonatal-tetanus</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Neonatal Tetanus</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>BR-PA</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Pará, Brazil</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>D030</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Neonatal Tetanus</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>新生儿破伤风</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>2014-04-01</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>2014-04</t>
+        </is>
+      </c>
+      <c r="N67" t="n">
+        <v>0</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0</v>
+      </c>
+      <c r="R67" t="n">
+        <v>0</v>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP67" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR67" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS67" t="inlineStr"/>
+      <c r="AT67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV67" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA67" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB67" t="inlineStr"/>
+      <c r="BC67" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>D030</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>neonatal-tetanus</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Neonatal Tetanus</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>BR-PB</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Paraíba, Brazil</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>D030</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Neonatal Tetanus</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>新生儿破伤风</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>2014-04-01</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>2014-04</t>
+        </is>
+      </c>
+      <c r="N68" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" t="n">
+        <v>0</v>
+      </c>
+      <c r="R68" t="n">
+        <v>0</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP68" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR68" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS68" t="inlineStr"/>
+      <c r="AT68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV68" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA68" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB68" t="inlineStr"/>
+      <c r="BC68" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>D030</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>neonatal-tetanus</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Neonatal Tetanus</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>BR-PE</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Pernambuco, Brazil</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>D030</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Neonatal Tetanus</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>新生儿破伤风</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>2014-04-01</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>2014-04</t>
+        </is>
+      </c>
+      <c r="N69" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" t="n">
+        <v>0</v>
+      </c>
+      <c r="R69" t="n">
+        <v>0</v>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP69" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR69" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS69" t="inlineStr"/>
+      <c r="AT69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV69" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA69" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB69" t="inlineStr"/>
+      <c r="BC69" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>D030</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>neonatal-tetanus</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Neonatal Tetanus</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>BR-PI</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Piauí, Brazil</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>D030</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Neonatal Tetanus</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>新生儿破伤风</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>2014-04-01</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>2014-04</t>
+        </is>
+      </c>
+      <c r="N70" t="n">
+        <v>0</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0</v>
+      </c>
+      <c r="R70" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP70" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR70" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS70" t="inlineStr"/>
+      <c r="AT70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV70" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA70" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB70" t="inlineStr"/>
+      <c r="BC70" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>D030</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>neonatal-tetanus</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Neonatal Tetanus</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>BR-PR</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Paraná, Brazil</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>D030</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Neonatal Tetanus</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>新生儿破伤风</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>2014-04-01</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>2014-04</t>
+        </is>
+      </c>
+      <c r="N71" t="n">
+        <v>0</v>
+      </c>
+      <c r="O71" t="n">
+        <v>0</v>
+      </c>
+      <c r="R71" t="n">
+        <v>0</v>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP71" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR71" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS71" t="inlineStr"/>
+      <c r="AT71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV71" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA71" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB71" t="inlineStr"/>
+      <c r="BC71" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>D030</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>neonatal-tetanus</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Neonatal Tetanus</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>BR-RJ</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro, Brazil</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>D030</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Neonatal Tetanus</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>新生儿破伤风</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>2014-04-01</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>2014-04</t>
+        </is>
+      </c>
+      <c r="N72" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP72" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR72" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS72" t="inlineStr"/>
+      <c r="AT72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV72" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA72" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB72" t="inlineStr"/>
+      <c r="BC72" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>D030</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>neonatal-tetanus</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Neonatal Tetanus</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>BR-RN</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Rio Grande do Norte, Brazil</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>D030</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Neonatal Tetanus</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>新生儿破伤风</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>2014-04-01</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>2014-04</t>
+        </is>
+      </c>
+      <c r="N73" t="n">
+        <v>0</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" t="n">
+        <v>0</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP73" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR73" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS73" t="inlineStr"/>
+      <c r="AT73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV73" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA73" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB73" t="inlineStr"/>
+      <c r="BC73" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>D030</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>neonatal-tetanus</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Neonatal Tetanus</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>BR-RO</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Rondônia, Brazil</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>D030</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Neonatal Tetanus</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>新生儿破伤风</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>2014-04-01</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>2014-04</t>
+        </is>
+      </c>
+      <c r="N74" t="n">
+        <v>0</v>
+      </c>
+      <c r="O74" t="n">
+        <v>0</v>
+      </c>
+      <c r="R74" t="n">
+        <v>0</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP74" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR74" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS74" t="inlineStr"/>
+      <c r="AT74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV74" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA74" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB74" t="inlineStr"/>
+      <c r="BC74" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>D030</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>neonatal-tetanus</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Neonatal Tetanus</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>BR-RR</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Roraima, Brazil</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>D030</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Neonatal Tetanus</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>新生儿破伤风</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>2014-04-01</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>2014-04</t>
+        </is>
+      </c>
+      <c r="N75" t="n">
+        <v>0</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP75" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR75" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS75" t="inlineStr"/>
+      <c r="AT75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV75" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA75" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB75" t="inlineStr"/>
+      <c r="BC75" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>D030</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>neonatal-tetanus</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Neonatal Tetanus</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>BR-RS</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Rio Grande do Sul, Brazil</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>D030</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Neonatal Tetanus</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>新生儿破伤风</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>2014-04-01</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>2014-04</t>
+        </is>
+      </c>
+      <c r="N76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0</v>
+      </c>
+      <c r="R76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP76" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR76" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS76" t="inlineStr"/>
+      <c r="AT76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV76" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA76" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB76" t="inlineStr"/>
+      <c r="BC76" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>D030</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>neonatal-tetanus</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Neonatal Tetanus</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>BR-SC</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Santa Catarina, Brazil</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>D030</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Neonatal Tetanus</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>新生儿破伤风</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>2014-04-01</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>2014-04</t>
+        </is>
+      </c>
+      <c r="N77" t="n">
+        <v>0</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0</v>
+      </c>
+      <c r="R77" t="n">
+        <v>0</v>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP77" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR77" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS77" t="inlineStr"/>
+      <c r="AT77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV77" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA77" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB77" t="inlineStr"/>
+      <c r="BC77" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>D030</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>neonatal-tetanus</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Neonatal Tetanus</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>BR-SE</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Sergipe, Brazil</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>D030</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Neonatal Tetanus</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>新生儿破伤风</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>2014-04-01</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>2014-04</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0</v>
+      </c>
+      <c r="R78" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP78" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR78" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS78" t="inlineStr"/>
+      <c r="AT78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV78" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA78" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB78" t="inlineStr"/>
+      <c r="BC78" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>D030</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>neonatal-tetanus</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Neonatal Tetanus</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>BR-SP</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>São Paulo, Brazil</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>D030</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Neonatal Tetanus</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>新生儿破伤风</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>2014-04-01</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>2014-04</t>
+        </is>
+      </c>
+      <c r="N79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0</v>
+      </c>
+      <c r="R79" t="n">
+        <v>0</v>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP79" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR79" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS79" t="inlineStr"/>
+      <c r="AT79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV79" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA79" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB79" t="inlineStr"/>
+      <c r="BC79" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>D030</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>neonatal-tetanus</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Neonatal Tetanus</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>BR-TO</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Tocantins, Brazil</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>D030</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Neonatal Tetanus</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>新生儿破伤风</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>2014-04-01</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>2014-04</t>
+        </is>
+      </c>
+      <c r="N80" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0</v>
+      </c>
+      <c r="R80" t="n">
+        <v>0</v>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP80" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR80" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS80" t="inlineStr"/>
+      <c r="AT80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV80" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA80" t="inlineStr">
+        <is>
+          <t>All Sources</t>
+        </is>
+      </c>
+      <c r="BB80" t="inlineStr"/>
+      <c r="BC80" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>D030</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>neonatal-tetanus</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Neonatal Tetanus</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>D030</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Neonatal Tetanus</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>新生儿破伤风</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>2014-04-01</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>2014-04</t>
+        </is>
+      </c>
+      <c r="N81" t="n">
+        <v>36</v>
+      </c>
+      <c r="O81" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>2</v>
+      </c>
+      <c r="R81" t="n">
+        <v>0.002615404733882568</v>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>nbs_computed</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP81" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR81" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS81" t="inlineStr"/>
+      <c r="AT81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV81" t="inlineStr">
+        <is>
           <t>cdc_weekly</t>
         </is>
       </c>
-      <c r="AW62" t="inlineStr">
+      <c r="AW81" t="inlineStr">
         <is>
           <t>China CDC Weekly</t>
         </is>
       </c>
-      <c r="AX62" t="inlineStr">
+      <c r="AX81" t="inlineStr">
         <is>
           <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
-      <c r="AY62" t="inlineStr">
+      <c r="AY81" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ62" t="inlineStr">
+      <c r="AZ81" t="inlineStr">
         <is>
           <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
-      <c r="BA62" t="inlineStr">
+      <c r="BA81" t="inlineStr">
         <is>
           <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
-      <c r="BB62" t="inlineStr">
+      <c r="BB81" t="inlineStr">
         <is>
           <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
-      <c r="BC62" t="inlineStr">
+      <c r="BC81" t="inlineStr">
+        <is>
+          <t>web; web; web</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>D030</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>neonatal-tetanus</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Neonatal Tetanus</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>D030</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Neonatal Tetanus</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>新生儿破伤风</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>2014-05-01</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>2014-05</t>
+        </is>
+      </c>
+      <c r="N82" t="n">
+        <v>27</v>
+      </c>
+      <c r="O82" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>1</v>
+      </c>
+      <c r="R82" t="n">
+        <v>0.001961553550411926</v>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>nbs_computed</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP82" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR82" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS82" t="inlineStr"/>
+      <c r="AT82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV82" t="inlineStr">
+        <is>
+          <t>cdc_weekly</t>
+        </is>
+      </c>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>China CDC Weekly</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>https://weekly.chinacdc.cn</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>cdc_weekly; nhc; pubmed</t>
+        </is>
+      </c>
+      <c r="BA82" t="inlineStr">
+        <is>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+        </is>
+      </c>
+      <c r="BB82" t="inlineStr">
+        <is>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+        </is>
+      </c>
+      <c r="BC82" t="inlineStr">
+        <is>
+          <t>web; web; web</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>D030</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>neonatal-tetanus</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Neonatal Tetanus</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>D030</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Neonatal Tetanus</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>新生儿破伤风</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>2014-06-01</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>2014-06</t>
+        </is>
+      </c>
+      <c r="N83" t="n">
+        <v>28</v>
+      </c>
+      <c r="O83" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>0</v>
+      </c>
+      <c r="R83" t="n">
+        <v>0.002034203681908664</v>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>nbs_computed</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP83" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR83" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS83" t="inlineStr"/>
+      <c r="AT83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV83" t="inlineStr">
+        <is>
+          <t>cdc_weekly</t>
+        </is>
+      </c>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>China CDC Weekly</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>https://weekly.chinacdc.cn</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>cdc_weekly; nhc; pubmed</t>
+        </is>
+      </c>
+      <c r="BA83" t="inlineStr">
+        <is>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+        </is>
+      </c>
+      <c r="BB83" t="inlineStr">
+        <is>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+        </is>
+      </c>
+      <c r="BC83" t="inlineStr">
+        <is>
+          <t>web; web; web</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>D030</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>neonatal-tetanus</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Neonatal Tetanus</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>D030</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Neonatal Tetanus</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>新生儿破伤风</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>2014-07-01</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>2014-07</t>
+        </is>
+      </c>
+      <c r="N84" t="n">
+        <v>51</v>
+      </c>
+      <c r="O84" t="n">
+        <v>51</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>2</v>
+      </c>
+      <c r="R84" t="n">
+        <v>0.003705156706333639</v>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>nbs_computed</t>
+        </is>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP84" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR84" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS84" t="inlineStr"/>
+      <c r="AT84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV84" t="inlineStr">
+        <is>
+          <t>cdc_weekly</t>
+        </is>
+      </c>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>China CDC Weekly</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>https://weekly.chinacdc.cn</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>cdc_weekly; nhc; pubmed</t>
+        </is>
+      </c>
+      <c r="BA84" t="inlineStr">
+        <is>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+        </is>
+      </c>
+      <c r="BB84" t="inlineStr">
+        <is>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+        </is>
+      </c>
+      <c r="BC84" t="inlineStr">
+        <is>
+          <t>web; web; web</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>D030</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>neonatal-tetanus</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Neonatal Tetanus</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>D030</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Neonatal Tetanus</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>新生儿破伤风</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>2014-08-01</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>2014-08</t>
+        </is>
+      </c>
+      <c r="N85" t="n">
+        <v>32</v>
+      </c>
+      <c r="O85" t="n">
+        <v>32</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>1</v>
+      </c>
+      <c r="R85" t="n">
+        <v>0.002324804207895616</v>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>nbs_computed</t>
+        </is>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP85" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR85" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS85" t="inlineStr"/>
+      <c r="AT85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV85" t="inlineStr">
+        <is>
+          <t>cdc_weekly</t>
+        </is>
+      </c>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>China CDC Weekly</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>https://weekly.chinacdc.cn</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>cdc_weekly; nhc; pubmed</t>
+        </is>
+      </c>
+      <c r="BA85" t="inlineStr">
+        <is>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+        </is>
+      </c>
+      <c r="BB85" t="inlineStr">
+        <is>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+        </is>
+      </c>
+      <c r="BC85" t="inlineStr">
+        <is>
+          <t>web; web; web</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>D030</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>neonatal-tetanus</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Neonatal Tetanus</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>D030</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Neonatal Tetanus</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>新生儿破伤风</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>2014-09-01</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>2014-09</t>
+        </is>
+      </c>
+      <c r="N86" t="n">
+        <v>58</v>
+      </c>
+      <c r="O86" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>2</v>
+      </c>
+      <c r="R86" t="n">
+        <v>0.004213707626810804</v>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>nbs_computed</t>
+        </is>
+      </c>
+      <c r="AO86" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP86" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR86" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS86" t="inlineStr"/>
+      <c r="AT86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV86" t="inlineStr">
+        <is>
+          <t>cdc_weekly</t>
+        </is>
+      </c>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>China CDC Weekly</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>https://weekly.chinacdc.cn</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>cdc_weekly; nhc; pubmed</t>
+        </is>
+      </c>
+      <c r="BA86" t="inlineStr">
+        <is>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+        </is>
+      </c>
+      <c r="BB86" t="inlineStr">
+        <is>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+        </is>
+      </c>
+      <c r="BC86" t="inlineStr">
+        <is>
+          <t>web; web; web</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>D030</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>neonatal-tetanus</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Neonatal Tetanus</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>D030</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Neonatal Tetanus</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>新生儿破伤风</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>2014-10-01</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>2014-10</t>
+        </is>
+      </c>
+      <c r="N87" t="n">
+        <v>42</v>
+      </c>
+      <c r="O87" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>1</v>
+      </c>
+      <c r="R87" t="n">
+        <v>0.003051305522862997</v>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>nbs_computed</t>
+        </is>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP87" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR87" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS87" t="inlineStr"/>
+      <c r="AT87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV87" t="inlineStr">
+        <is>
+          <t>cdc_weekly</t>
+        </is>
+      </c>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>China CDC Weekly</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>https://weekly.chinacdc.cn</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>cdc_weekly; nhc; pubmed</t>
+        </is>
+      </c>
+      <c r="BA87" t="inlineStr">
+        <is>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+        </is>
+      </c>
+      <c r="BB87" t="inlineStr">
+        <is>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+        </is>
+      </c>
+      <c r="BC87" t="inlineStr">
+        <is>
+          <t>web; web; web</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>D030</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>neonatal-tetanus</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Neonatal Tetanus</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>D030</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Neonatal Tetanus</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>新生儿破伤风</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>2014-11-01</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>2014-11</t>
+        </is>
+      </c>
+      <c r="N88" t="n">
+        <v>32</v>
+      </c>
+      <c r="O88" t="n">
+        <v>32</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>1</v>
+      </c>
+      <c r="R88" t="n">
+        <v>0.002324804207895616</v>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>nbs_computed</t>
+        </is>
+      </c>
+      <c r="AO88" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP88" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR88" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS88" t="inlineStr"/>
+      <c r="AT88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV88" t="inlineStr">
+        <is>
+          <t>cdc_weekly</t>
+        </is>
+      </c>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>China CDC Weekly</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>https://weekly.chinacdc.cn</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>cdc_weekly; nhc; pubmed</t>
+        </is>
+      </c>
+      <c r="BA88" t="inlineStr">
+        <is>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+        </is>
+      </c>
+      <c r="BB88" t="inlineStr">
+        <is>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+        </is>
+      </c>
+      <c r="BC88" t="inlineStr">
+        <is>
+          <t>web; web; web</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>D030</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>neonatal-tetanus</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Neonatal Tetanus</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>D030</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Neonatal Tetanus</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>新生儿破伤风</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>2014-12-01</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>2014-12</t>
+        </is>
+      </c>
+      <c r="N89" t="n">
+        <v>34</v>
+      </c>
+      <c r="O89" t="n">
+        <v>34</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>1</v>
+      </c>
+      <c r="R89" t="n">
+        <v>0.002470104470889092</v>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>nbs_computed</t>
+        </is>
+      </c>
+      <c r="AO89" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP89" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR89" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS89" t="inlineStr"/>
+      <c r="AT89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV89" t="inlineStr">
+        <is>
+          <t>cdc_weekly</t>
+        </is>
+      </c>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>China CDC Weekly</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>https://weekly.chinacdc.cn</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>cdc_weekly; nhc; pubmed</t>
+        </is>
+      </c>
+      <c r="BA89" t="inlineStr">
+        <is>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+        </is>
+      </c>
+      <c r="BB89" t="inlineStr">
+        <is>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+        </is>
+      </c>
+      <c r="BC89" t="inlineStr">
         <is>
           <t>web; web; web</t>
         </is>
@@ -9837,7 +13509,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>61</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10">
@@ -9847,7 +13519,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>61</v>
+        <v>88</v>
       </c>
     </row>
     <row r="11">
@@ -9899,7 +13571,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3693</v>
+        <v>3694</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d030/2010-2014.xlsx
+++ b/diseases/d030/2010-2014.xlsx
@@ -776,6 +776,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -924,6 +929,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1072,6 +1082,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1220,6 +1235,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1368,6 +1388,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1516,6 +1541,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1664,6 +1694,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1812,6 +1847,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1960,6 +2000,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2108,6 +2153,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2256,6 +2306,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2404,6 +2459,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2552,6 +2612,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2700,6 +2765,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2848,6 +2918,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2996,6 +3071,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3144,6 +3224,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3292,6 +3377,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3440,6 +3530,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3588,6 +3683,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3736,6 +3836,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3884,6 +3989,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4032,6 +4142,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4180,6 +4295,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4328,6 +4448,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4476,6 +4601,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4624,6 +4754,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4772,6 +4907,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4920,6 +5060,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5068,6 +5213,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5216,6 +5366,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5364,6 +5519,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5512,6 +5672,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5660,6 +5825,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5808,6 +5978,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5956,6 +6131,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6104,6 +6284,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6252,6 +6437,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6400,6 +6590,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6548,6 +6743,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6696,6 +6896,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6844,6 +7049,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6992,6 +7202,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7140,6 +7355,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7288,6 +7508,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7436,6 +7661,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7584,6 +7814,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7732,6 +7967,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7880,6 +8120,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8028,6 +8273,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8176,6 +8426,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12144,6 +12399,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO81" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12292,6 +12552,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO82" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12440,6 +12705,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO83" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12588,6 +12858,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO84" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12736,6 +13011,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO85" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12884,6 +13164,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO86" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13032,6 +13317,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO87" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13180,6 +13470,11 @@
           <t>nbs_computed</t>
         </is>
       </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13326,6 +13621,11 @@
       <c r="S89" t="inlineStr">
         <is>
           <t>nbs_computed</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">

--- a/diseases/d030/2010-2014.xlsx
+++ b/diseases/d030/2010-2014.xlsx
@@ -771,11 +771,6 @@
       <c r="R2" t="n">
         <v>0.006637283635739908</v>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -788,22 +783,12 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
@@ -924,11 +909,6 @@
       <c r="R3" t="n">
         <v>0.006040673870729579</v>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -941,22 +921,12 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
@@ -1077,11 +1047,6 @@
       <c r="R4" t="n">
         <v>0.007905079386386855</v>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1094,22 +1059,12 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
@@ -1230,11 +1185,6 @@
       <c r="R5" t="n">
         <v>0.006338978753234743</v>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1247,22 +1197,12 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
@@ -1383,11 +1323,6 @@
       <c r="R6" t="n">
         <v>0.004996606781961504</v>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1400,22 +1335,12 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
@@ -1536,11 +1461,6 @@
       <c r="R7" t="n">
         <v>0.007755926945134274</v>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1553,22 +1473,12 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
@@ -1689,11 +1599,6 @@
       <c r="R8" t="n">
         <v>0.007084740959497655</v>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1706,22 +1611,12 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
@@ -1842,11 +1737,6 @@
       <c r="R9" t="n">
         <v>0.007905079386386855</v>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1859,22 +1749,12 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
@@ -1995,11 +1875,6 @@
       <c r="R10" t="n">
         <v>0.008949146475154933</v>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2012,22 +1887,12 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
@@ -2148,11 +2013,6 @@
       <c r="R11" t="n">
         <v>0.008949146475154933</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2165,22 +2025,12 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
@@ -2301,11 +2151,6 @@
       <c r="R12" t="n">
         <v>0.007755926945134274</v>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2318,22 +2163,12 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
@@ -2454,11 +2289,6 @@
       <c r="R13" t="n">
         <v>0.00678643607699249</v>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2471,22 +2301,12 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
@@ -2607,11 +2427,6 @@
       <c r="R14" t="n">
         <v>0.006077855851048059</v>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2624,22 +2439,12 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
@@ -2760,11 +2565,6 @@
       <c r="R15" t="n">
         <v>0.004224851018411456</v>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2777,22 +2577,12 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -2913,11 +2703,6 @@
       <c r="R16" t="n">
         <v>0.004224851018411456</v>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2930,22 +2715,12 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
@@ -3066,11 +2841,6 @@
       <c r="R17" t="n">
         <v>0.00429897121171692</v>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3083,22 +2853,12 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
@@ -3219,11 +2979,6 @@
       <c r="R18" t="n">
         <v>0.005262533724687954</v>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3236,22 +2991,12 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
-      </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
@@ -3372,11 +3117,6 @@
       <c r="R19" t="n">
         <v>0.004891932758160633</v>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3389,22 +3129,12 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
-      </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
@@ -3525,11 +3255,6 @@
       <c r="R20" t="n">
         <v>0.005559014497909811</v>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3542,22 +3267,12 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
-      </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
@@ -3678,11 +3393,6 @@
       <c r="R21" t="n">
         <v>0.00644845681757538</v>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3695,22 +3405,12 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
-      </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
@@ -3831,11 +3531,6 @@
       <c r="R22" t="n">
         <v>0.004817812564855169</v>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3848,22 +3543,12 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
         <v>0</v>
-      </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
@@ -3984,11 +3669,6 @@
       <c r="R23" t="n">
         <v>0.006819057784102701</v>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4001,22 +3681,12 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
-      </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
@@ -4137,11 +3807,6 @@
       <c r="R24" t="n">
         <v>0.005633134691215275</v>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4154,22 +3819,12 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR24" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
         <v>0</v>
-      </c>
-      <c r="AU24" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
@@ -4290,11 +3945,6 @@
       <c r="R25" t="n">
         <v>0.004891932758160633</v>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4307,22 +3957,12 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR25" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
         <v>0</v>
-      </c>
-      <c r="AU25" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
@@ -4443,11 +4083,6 @@
       <c r="R26" t="n">
         <v>0.004561439649210577</v>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4460,22 +4095,12 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR26" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
         <v>0</v>
-      </c>
-      <c r="AU26" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
@@ -4596,11 +4221,6 @@
       <c r="R27" t="n">
         <v>0.003678580362266594</v>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4613,22 +4233,12 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR27" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
         <v>0</v>
-      </c>
-      <c r="AU27" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
@@ -4749,11 +4359,6 @@
       <c r="R28" t="n">
         <v>0.004561439649210577</v>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4766,22 +4371,12 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR28" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="n">
         <v>0</v>
-      </c>
-      <c r="AU28" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
@@ -4902,11 +4497,6 @@
       <c r="R29" t="n">
         <v>0.003605008755021262</v>
       </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4919,22 +4509,12 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR29" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
         <v>0</v>
-      </c>
-      <c r="AU29" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
@@ -5055,11 +4635,6 @@
       <c r="R30" t="n">
         <v>0.004340724827474581</v>
       </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5072,22 +4647,12 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR30" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="n">
         <v>0</v>
-      </c>
-      <c r="AU30" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
@@ -5208,11 +4773,6 @@
       <c r="R31" t="n">
         <v>0.00426715322022925</v>
       </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5225,22 +4785,12 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR31" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
         <v>0</v>
-      </c>
-      <c r="AU31" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
@@ -5361,11 +4911,6 @@
       <c r="R32" t="n">
         <v>0.004708582863701241</v>
       </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5378,22 +4923,12 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR32" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
         <v>0</v>
-      </c>
-      <c r="AU32" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
@@ -5514,11 +5049,6 @@
       <c r="R33" t="n">
         <v>0.004708582863701241</v>
       </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5531,22 +5061,12 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR33" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="n">
         <v>0</v>
-      </c>
-      <c r="AU33" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
@@ -5667,11 +5187,6 @@
       <c r="R34" t="n">
         <v>0.004561439649210577</v>
       </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5684,22 +5199,12 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR34" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="n">
         <v>0</v>
-      </c>
-      <c r="AU34" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
@@ -5820,11 +5325,6 @@
       <c r="R35" t="n">
         <v>0.005370727328909228</v>
       </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5837,22 +5337,12 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR35" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="n">
         <v>0</v>
-      </c>
-      <c r="AU35" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
@@ -5973,11 +5463,6 @@
       <c r="R36" t="n">
         <v>0.004046438398493253</v>
       </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5990,22 +5475,12 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR36" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="n">
         <v>0</v>
-      </c>
-      <c r="AU36" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
@@ -6126,11 +5601,6 @@
       <c r="R37" t="n">
         <v>0.00353143714777593</v>
       </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6143,22 +5613,12 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR37" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="n">
         <v>0</v>
-      </c>
-      <c r="AU37" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
@@ -6279,11 +5739,6 @@
       <c r="R38" t="n">
         <v>0.004168921785176191</v>
       </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6296,22 +5751,12 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR38" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="n">
         <v>0</v>
-      </c>
-      <c r="AU38" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
@@ -6432,11 +5877,6 @@
       <c r="R39" t="n">
         <v>0.002852420168804763</v>
       </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6449,22 +5889,12 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR39" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="n">
         <v>0</v>
-      </c>
-      <c r="AU39" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV39" t="inlineStr">
         <is>
@@ -6585,11 +6015,6 @@
       <c r="R40" t="n">
         <v>0.002852420168804763</v>
       </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6602,22 +6027,12 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR40" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="n">
         <v>0</v>
-      </c>
-      <c r="AU40" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV40" t="inlineStr">
         <is>
@@ -6738,11 +6153,6 @@
       <c r="R41" t="n">
         <v>0.003291254040928572</v>
       </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6755,22 +6165,12 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR41" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="n">
         <v>0</v>
-      </c>
-      <c r="AU41" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
@@ -6891,11 +6291,6 @@
       <c r="R42" t="n">
         <v>0.002852420168804763</v>
       </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6908,22 +6303,12 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR42" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="n">
         <v>0</v>
-      </c>
-      <c r="AU42" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
@@ -7044,11 +6429,6 @@
       <c r="R43" t="n">
         <v>0.003218115062241271</v>
       </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7061,22 +6441,12 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR43" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="n">
         <v>0</v>
-      </c>
-      <c r="AU43" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
@@ -7197,11 +6567,6 @@
       <c r="R44" t="n">
         <v>0.003437531998303176</v>
       </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7214,22 +6579,12 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR44" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="n">
         <v>0</v>
-      </c>
-      <c r="AU44" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
@@ -7350,11 +6705,6 @@
       <c r="R45" t="n">
         <v>0.003803226891739684</v>
       </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7367,22 +6717,12 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR45" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="n">
         <v>0</v>
-      </c>
-      <c r="AU45" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
@@ -7503,11 +6843,6 @@
       <c r="R46" t="n">
         <v>0.003437531998303176</v>
       </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7520,22 +6855,12 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR46" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="n">
         <v>0</v>
-      </c>
-      <c r="AU46" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV46" t="inlineStr">
         <is>
@@ -7656,11 +6981,6 @@
       <c r="R47" t="n">
         <v>0.003510670976990478</v>
       </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7673,22 +6993,12 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR47" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="n">
         <v>0</v>
-      </c>
-      <c r="AU47" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV47" t="inlineStr">
         <is>
@@ -7809,11 +7119,6 @@
       <c r="R48" t="n">
         <v>0.002779281190117461</v>
       </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7826,22 +7131,12 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR48" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="n">
         <v>0</v>
-      </c>
-      <c r="AU48" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV48" t="inlineStr">
         <is>
@@ -7962,11 +7257,6 @@
       <c r="R49" t="n">
         <v>0.002340447317993652</v>
       </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7979,22 +7269,12 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR49" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="n">
         <v>0</v>
-      </c>
-      <c r="AU49" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
@@ -8115,11 +7395,6 @@
       <c r="R50" t="n">
         <v>0.002760704996876044</v>
       </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8132,22 +7407,12 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR50" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="n">
         <v>0</v>
-      </c>
-      <c r="AU50" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV50" t="inlineStr">
         <is>
@@ -8268,11 +7533,6 @@
       <c r="R51" t="n">
         <v>0.001888903418915188</v>
       </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8285,22 +7545,12 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR51" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="n">
         <v>0</v>
-      </c>
-      <c r="AU51" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV51" t="inlineStr">
         <is>
@@ -8421,11 +7671,6 @@
       <c r="R52" t="n">
         <v>0.00254275460238583</v>
       </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8438,22 +7683,12 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR52" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="n">
         <v>0</v>
-      </c>
-      <c r="AU52" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV52" t="inlineStr">
         <is>
@@ -8574,9 +7809,9 @@
       <c r="R53" t="n">
         <v>0.0004931730985003484</v>
       </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
@@ -8586,22 +7821,12 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR53" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="n">
         <v>0</v>
-      </c>
-      <c r="AU53" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
@@ -8719,9 +7944,9 @@
       <c r="R54" t="n">
         <v>0</v>
       </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
@@ -8731,22 +7956,12 @@
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR54" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="n">
         <v>0</v>
-      </c>
-      <c r="AU54" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV54" t="inlineStr">
         <is>
@@ -8855,9 +8070,9 @@
       <c r="R55" t="n">
         <v>0</v>
       </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
@@ -8867,22 +8082,12 @@
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR55" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="n">
         <v>0</v>
-      </c>
-      <c r="AU55" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
@@ -8991,9 +8196,9 @@
       <c r="R56" t="n">
         <v>0</v>
       </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
@@ -9003,22 +8208,12 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR56" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="n">
         <v>0</v>
-      </c>
-      <c r="AU56" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
@@ -9127,9 +8322,9 @@
       <c r="R57" t="n">
         <v>0</v>
       </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
@@ -9139,22 +8334,12 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR57" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="n">
         <v>0</v>
-      </c>
-      <c r="AU57" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
@@ -9263,9 +8448,9 @@
       <c r="R58" t="n">
         <v>0</v>
       </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
@@ -9275,22 +8460,12 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR58" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="n">
         <v>0</v>
-      </c>
-      <c r="AU58" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV58" t="inlineStr">
         <is>
@@ -9399,9 +8574,9 @@
       <c r="R59" t="n">
         <v>0</v>
       </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
@@ -9411,22 +8586,12 @@
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR59" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="n">
         <v>0</v>
-      </c>
-      <c r="AU59" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
@@ -9535,9 +8700,9 @@
       <c r="R60" t="n">
         <v>0</v>
       </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
@@ -9547,22 +8712,12 @@
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR60" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="n">
         <v>0</v>
-      </c>
-      <c r="AU60" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV60" t="inlineStr">
         <is>
@@ -9671,9 +8826,9 @@
       <c r="R61" t="n">
         <v>0</v>
       </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
@@ -9683,22 +8838,12 @@
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR61" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="n">
         <v>0</v>
-      </c>
-      <c r="AU61" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV61" t="inlineStr">
         <is>
@@ -9807,9 +8952,9 @@
       <c r="R62" t="n">
         <v>0</v>
       </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
@@ -9819,22 +8964,12 @@
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR62" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="n">
         <v>0</v>
-      </c>
-      <c r="AU62" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV62" t="inlineStr">
         <is>
@@ -9943,9 +9078,9 @@
       <c r="R63" t="n">
         <v>0</v>
       </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
@@ -9955,22 +9090,12 @@
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR63" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="n">
         <v>0</v>
-      </c>
-      <c r="AU63" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV63" t="inlineStr">
         <is>
@@ -10079,9 +9204,9 @@
       <c r="R64" t="n">
         <v>0.004822973481796675</v>
       </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
@@ -10091,22 +9216,12 @@
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR64" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="n">
         <v>0</v>
-      </c>
-      <c r="AU64" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV64" t="inlineStr">
         <is>
@@ -10215,9 +9330,9 @@
       <c r="R65" t="n">
         <v>0</v>
       </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
@@ -10227,22 +9342,12 @@
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR65" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="n">
         <v>0</v>
-      </c>
-      <c r="AU65" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV65" t="inlineStr">
         <is>
@@ -10351,9 +9456,9 @@
       <c r="R66" t="n">
         <v>0</v>
       </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
@@ -10363,22 +9468,12 @@
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR66" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS66" t="inlineStr"/>
       <c r="AT66" t="n">
         <v>0</v>
-      </c>
-      <c r="AU66" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV66" t="inlineStr">
         <is>
@@ -10487,9 +9582,9 @@
       <c r="R67" t="n">
         <v>0</v>
       </c>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
@@ -10499,22 +9594,12 @@
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR67" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="n">
         <v>0</v>
-      </c>
-      <c r="AU67" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV67" t="inlineStr">
         <is>
@@ -10623,9 +9708,9 @@
       <c r="R68" t="n">
         <v>0</v>
       </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
@@ -10635,22 +9720,12 @@
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR68" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="n">
         <v>0</v>
-      </c>
-      <c r="AU68" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV68" t="inlineStr">
         <is>
@@ -10759,9 +9834,9 @@
       <c r="R69" t="n">
         <v>0</v>
       </c>
-      <c r="S69" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
@@ -10771,22 +9846,12 @@
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR69" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="n">
         <v>0</v>
-      </c>
-      <c r="AU69" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV69" t="inlineStr">
         <is>
@@ -10895,9 +9960,9 @@
       <c r="R70" t="n">
         <v>0</v>
       </c>
-      <c r="S70" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
@@ -10907,22 +9972,12 @@
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR70" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="n">
         <v>0</v>
-      </c>
-      <c r="AU70" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV70" t="inlineStr">
         <is>
@@ -11031,9 +10086,9 @@
       <c r="R71" t="n">
         <v>0</v>
       </c>
-      <c r="S71" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
@@ -11043,22 +10098,12 @@
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR71" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS71" t="inlineStr"/>
       <c r="AT71" t="n">
         <v>0</v>
-      </c>
-      <c r="AU71" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV71" t="inlineStr">
         <is>
@@ -11167,9 +10212,9 @@
       <c r="R72" t="n">
         <v>0</v>
       </c>
-      <c r="S72" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
@@ -11179,22 +10224,12 @@
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR72" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="n">
         <v>0</v>
-      </c>
-      <c r="AU72" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV72" t="inlineStr">
         <is>
@@ -11303,9 +10338,9 @@
       <c r="R73" t="n">
         <v>0</v>
       </c>
-      <c r="S73" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
@@ -11315,22 +10350,12 @@
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR73" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS73" t="inlineStr"/>
       <c r="AT73" t="n">
         <v>0</v>
-      </c>
-      <c r="AU73" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV73" t="inlineStr">
         <is>
@@ -11439,9 +10464,9 @@
       <c r="R74" t="n">
         <v>0</v>
       </c>
-      <c r="S74" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
@@ -11451,22 +10476,12 @@
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR74" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="n">
         <v>0</v>
-      </c>
-      <c r="AU74" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV74" t="inlineStr">
         <is>
@@ -11575,9 +10590,9 @@
       <c r="R75" t="n">
         <v>0</v>
       </c>
-      <c r="S75" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
@@ -11587,22 +10602,12 @@
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR75" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="n">
         <v>0</v>
-      </c>
-      <c r="AU75" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV75" t="inlineStr">
         <is>
@@ -11711,9 +10716,9 @@
       <c r="R76" t="n">
         <v>0</v>
       </c>
-      <c r="S76" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
@@ -11723,22 +10728,12 @@
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR76" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS76" t="inlineStr"/>
       <c r="AT76" t="n">
         <v>0</v>
-      </c>
-      <c r="AU76" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV76" t="inlineStr">
         <is>
@@ -11847,9 +10842,9 @@
       <c r="R77" t="n">
         <v>0</v>
       </c>
-      <c r="S77" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
@@ -11859,22 +10854,12 @@
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR77" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS77" t="inlineStr"/>
       <c r="AT77" t="n">
         <v>0</v>
-      </c>
-      <c r="AU77" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV77" t="inlineStr">
         <is>
@@ -11983,9 +10968,9 @@
       <c r="R78" t="n">
         <v>0</v>
       </c>
-      <c r="S78" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
@@ -11995,22 +10980,12 @@
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR78" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="n">
         <v>0</v>
-      </c>
-      <c r="AU78" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV78" t="inlineStr">
         <is>
@@ -12119,9 +11094,9 @@
       <c r="R79" t="n">
         <v>0</v>
       </c>
-      <c r="S79" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
@@ -12131,22 +11106,12 @@
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR79" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS79" t="inlineStr"/>
       <c r="AT79" t="n">
         <v>0</v>
-      </c>
-      <c r="AU79" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV79" t="inlineStr">
         <is>
@@ -12255,9 +11220,9 @@
       <c r="R80" t="n">
         <v>0</v>
       </c>
-      <c r="S80" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
@@ -12267,22 +11232,12 @@
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR80" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS80" t="inlineStr"/>
       <c r="AT80" t="n">
         <v>0</v>
-      </c>
-      <c r="AU80" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV80" t="inlineStr">
         <is>
@@ -12394,11 +11349,6 @@
       <c r="R81" t="n">
         <v>0.002615404733882568</v>
       </c>
-      <c r="S81" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12411,22 +11361,12 @@
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR81" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="n">
         <v>0</v>
-      </c>
-      <c r="AU81" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV81" t="inlineStr">
         <is>
@@ -12547,11 +11487,6 @@
       <c r="R82" t="n">
         <v>0.001961553550411926</v>
       </c>
-      <c r="S82" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12564,22 +11499,12 @@
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR82" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS82" t="inlineStr"/>
       <c r="AT82" t="n">
         <v>0</v>
-      </c>
-      <c r="AU82" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV82" t="inlineStr">
         <is>
@@ -12700,11 +11625,6 @@
       <c r="R83" t="n">
         <v>0.002034203681908664</v>
       </c>
-      <c r="S83" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12717,22 +11637,12 @@
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR83" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="n">
         <v>0</v>
-      </c>
-      <c r="AU83" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV83" t="inlineStr">
         <is>
@@ -12853,11 +11763,6 @@
       <c r="R84" t="n">
         <v>0.003705156706333639</v>
       </c>
-      <c r="S84" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12870,22 +11775,12 @@
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR84" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS84" t="inlineStr"/>
       <c r="AT84" t="n">
         <v>0</v>
-      </c>
-      <c r="AU84" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV84" t="inlineStr">
         <is>
@@ -13006,11 +11901,6 @@
       <c r="R85" t="n">
         <v>0.002324804207895616</v>
       </c>
-      <c r="S85" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13023,22 +11913,12 @@
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR85" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="n">
         <v>0</v>
-      </c>
-      <c r="AU85" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV85" t="inlineStr">
         <is>
@@ -13159,11 +12039,6 @@
       <c r="R86" t="n">
         <v>0.004213707626810804</v>
       </c>
-      <c r="S86" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13176,22 +12051,12 @@
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR86" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS86" t="inlineStr"/>
       <c r="AT86" t="n">
         <v>0</v>
-      </c>
-      <c r="AU86" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV86" t="inlineStr">
         <is>
@@ -13312,11 +12177,6 @@
       <c r="R87" t="n">
         <v>0.003051305522862997</v>
       </c>
-      <c r="S87" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13329,22 +12189,12 @@
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR87" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="n">
         <v>0</v>
-      </c>
-      <c r="AU87" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV87" t="inlineStr">
         <is>
@@ -13465,11 +12315,6 @@
       <c r="R88" t="n">
         <v>0.002324804207895616</v>
       </c>
-      <c r="S88" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13482,22 +12327,12 @@
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR88" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS88" t="inlineStr"/>
       <c r="AT88" t="n">
         <v>0</v>
-      </c>
-      <c r="AU88" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV88" t="inlineStr">
         <is>
@@ -13618,11 +12453,6 @@
       <c r="R89" t="n">
         <v>0.002470104470889092</v>
       </c>
-      <c r="S89" t="inlineStr">
-        <is>
-          <t>nbs_computed</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13635,22 +12465,12 @@
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR89" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS89" t="inlineStr"/>
       <c r="AT89" t="n">
         <v>0</v>
-      </c>
-      <c r="AU89" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV89" t="inlineStr">
         <is>

--- a/diseases/d030/2010-2014.xlsx
+++ b/diseases/d030/2010-2014.xlsx
@@ -7809,9 +7809,9 @@
       <c r="R53" t="n">
         <v>0.0004931730985003484</v>
       </c>
-      <c r="AA53" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
@@ -7821,12 +7821,22 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR53" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="n">
         <v>0</v>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
@@ -7944,9 +7954,9 @@
       <c r="R54" t="n">
         <v>0</v>
       </c>
-      <c r="AA54" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
@@ -7956,13 +7966,23 @@
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR54" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="n">
         <v>0</v>
       </c>
+      <c r="AU54" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV54" t="inlineStr">
         <is>
           <t>all</t>
@@ -7973,6 +7993,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>web</t>
@@ -7988,7 +8013,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB54" t="inlineStr"/>
+      <c r="BB54" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC54" t="inlineStr">
         <is>
           <t>web</t>
@@ -8070,9 +8099,9 @@
       <c r="R55" t="n">
         <v>0</v>
       </c>
-      <c r="AA55" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
@@ -8082,13 +8111,23 @@
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR55" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="n">
         <v>0</v>
       </c>
+      <c r="AU55" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV55" t="inlineStr">
         <is>
           <t>all</t>
@@ -8099,6 +8138,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>web</t>
@@ -8114,7 +8158,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB55" t="inlineStr"/>
+      <c r="BB55" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC55" t="inlineStr">
         <is>
           <t>web</t>
@@ -8196,9 +8244,9 @@
       <c r="R56" t="n">
         <v>0</v>
       </c>
-      <c r="AA56" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
@@ -8208,13 +8256,23 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR56" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="n">
         <v>0</v>
       </c>
+      <c r="AU56" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV56" t="inlineStr">
         <is>
           <t>all</t>
@@ -8225,6 +8283,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>web</t>
@@ -8240,7 +8303,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB56" t="inlineStr"/>
+      <c r="BB56" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC56" t="inlineStr">
         <is>
           <t>web</t>
@@ -8322,9 +8389,9 @@
       <c r="R57" t="n">
         <v>0</v>
       </c>
-      <c r="AA57" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
@@ -8334,13 +8401,23 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR57" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="n">
         <v>0</v>
       </c>
+      <c r="AU57" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV57" t="inlineStr">
         <is>
           <t>all</t>
@@ -8351,6 +8428,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY57" t="inlineStr">
         <is>
           <t>web</t>
@@ -8366,7 +8448,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB57" t="inlineStr"/>
+      <c r="BB57" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC57" t="inlineStr">
         <is>
           <t>web</t>
@@ -8448,9 +8534,9 @@
       <c r="R58" t="n">
         <v>0</v>
       </c>
-      <c r="AA58" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
@@ -8460,13 +8546,23 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR58" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="n">
         <v>0</v>
       </c>
+      <c r="AU58" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV58" t="inlineStr">
         <is>
           <t>all</t>
@@ -8477,6 +8573,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY58" t="inlineStr">
         <is>
           <t>web</t>
@@ -8492,7 +8593,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB58" t="inlineStr"/>
+      <c r="BB58" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC58" t="inlineStr">
         <is>
           <t>web</t>
@@ -8574,9 +8679,9 @@
       <c r="R59" t="n">
         <v>0</v>
       </c>
-      <c r="AA59" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
@@ -8586,13 +8691,23 @@
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR59" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="n">
         <v>0</v>
       </c>
+      <c r="AU59" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV59" t="inlineStr">
         <is>
           <t>all</t>
@@ -8603,6 +8718,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY59" t="inlineStr">
         <is>
           <t>web</t>
@@ -8618,7 +8738,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB59" t="inlineStr"/>
+      <c r="BB59" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC59" t="inlineStr">
         <is>
           <t>web</t>
@@ -8700,9 +8824,9 @@
       <c r="R60" t="n">
         <v>0</v>
       </c>
-      <c r="AA60" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
@@ -8712,13 +8836,23 @@
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR60" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="n">
         <v>0</v>
       </c>
+      <c r="AU60" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV60" t="inlineStr">
         <is>
           <t>all</t>
@@ -8729,6 +8863,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY60" t="inlineStr">
         <is>
           <t>web</t>
@@ -8744,7 +8883,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB60" t="inlineStr"/>
+      <c r="BB60" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC60" t="inlineStr">
         <is>
           <t>web</t>
@@ -8826,9 +8969,9 @@
       <c r="R61" t="n">
         <v>0</v>
       </c>
-      <c r="AA61" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
@@ -8838,13 +8981,23 @@
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR61" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="n">
         <v>0</v>
       </c>
+      <c r="AU61" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV61" t="inlineStr">
         <is>
           <t>all</t>
@@ -8855,6 +9008,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY61" t="inlineStr">
         <is>
           <t>web</t>
@@ -8870,7 +9028,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB61" t="inlineStr"/>
+      <c r="BB61" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC61" t="inlineStr">
         <is>
           <t>web</t>
@@ -8952,9 +9114,9 @@
       <c r="R62" t="n">
         <v>0</v>
       </c>
-      <c r="AA62" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
@@ -8964,13 +9126,23 @@
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR62" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="n">
         <v>0</v>
       </c>
+      <c r="AU62" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV62" t="inlineStr">
         <is>
           <t>all</t>
@@ -8981,6 +9153,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY62" t="inlineStr">
         <is>
           <t>web</t>
@@ -8996,7 +9173,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB62" t="inlineStr"/>
+      <c r="BB62" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC62" t="inlineStr">
         <is>
           <t>web</t>
@@ -9078,9 +9259,9 @@
       <c r="R63" t="n">
         <v>0</v>
       </c>
-      <c r="AA63" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
@@ -9090,13 +9271,23 @@
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR63" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="n">
         <v>0</v>
       </c>
+      <c r="AU63" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV63" t="inlineStr">
         <is>
           <t>all</t>
@@ -9107,6 +9298,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY63" t="inlineStr">
         <is>
           <t>web</t>
@@ -9122,7 +9318,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB63" t="inlineStr"/>
+      <c r="BB63" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC63" t="inlineStr">
         <is>
           <t>web</t>
@@ -9204,9 +9404,9 @@
       <c r="R64" t="n">
         <v>0.004822973481796675</v>
       </c>
-      <c r="AA64" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
@@ -9216,13 +9416,23 @@
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR64" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="n">
         <v>0</v>
       </c>
+      <c r="AU64" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV64" t="inlineStr">
         <is>
           <t>all</t>
@@ -9233,6 +9443,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY64" t="inlineStr">
         <is>
           <t>web</t>
@@ -9248,7 +9463,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB64" t="inlineStr"/>
+      <c r="BB64" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC64" t="inlineStr">
         <is>
           <t>web</t>
@@ -9330,9 +9549,9 @@
       <c r="R65" t="n">
         <v>0</v>
       </c>
-      <c r="AA65" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
@@ -9342,13 +9561,23 @@
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR65" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="n">
         <v>0</v>
       </c>
+      <c r="AU65" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV65" t="inlineStr">
         <is>
           <t>all</t>
@@ -9359,6 +9588,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY65" t="inlineStr">
         <is>
           <t>web</t>
@@ -9374,7 +9608,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB65" t="inlineStr"/>
+      <c r="BB65" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC65" t="inlineStr">
         <is>
           <t>web</t>
@@ -9456,9 +9694,9 @@
       <c r="R66" t="n">
         <v>0</v>
       </c>
-      <c r="AA66" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
@@ -9468,13 +9706,23 @@
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR66" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS66" t="inlineStr"/>
       <c r="AT66" t="n">
         <v>0</v>
       </c>
+      <c r="AU66" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV66" t="inlineStr">
         <is>
           <t>all</t>
@@ -9485,6 +9733,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY66" t="inlineStr">
         <is>
           <t>web</t>
@@ -9500,7 +9753,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB66" t="inlineStr"/>
+      <c r="BB66" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC66" t="inlineStr">
         <is>
           <t>web</t>
@@ -9582,9 +9839,9 @@
       <c r="R67" t="n">
         <v>0</v>
       </c>
-      <c r="AA67" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
@@ -9594,13 +9851,23 @@
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR67" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="n">
         <v>0</v>
       </c>
+      <c r="AU67" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV67" t="inlineStr">
         <is>
           <t>all</t>
@@ -9611,6 +9878,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY67" t="inlineStr">
         <is>
           <t>web</t>
@@ -9626,7 +9898,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB67" t="inlineStr"/>
+      <c r="BB67" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC67" t="inlineStr">
         <is>
           <t>web</t>
@@ -9708,9 +9984,9 @@
       <c r="R68" t="n">
         <v>0</v>
       </c>
-      <c r="AA68" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
@@ -9720,13 +9996,23 @@
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR68" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="n">
         <v>0</v>
       </c>
+      <c r="AU68" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV68" t="inlineStr">
         <is>
           <t>all</t>
@@ -9737,6 +10023,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY68" t="inlineStr">
         <is>
           <t>web</t>
@@ -9752,7 +10043,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB68" t="inlineStr"/>
+      <c r="BB68" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC68" t="inlineStr">
         <is>
           <t>web</t>
@@ -9834,9 +10129,9 @@
       <c r="R69" t="n">
         <v>0</v>
       </c>
-      <c r="AA69" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
@@ -9846,13 +10141,23 @@
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR69" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="n">
         <v>0</v>
       </c>
+      <c r="AU69" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV69" t="inlineStr">
         <is>
           <t>all</t>
@@ -9863,6 +10168,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY69" t="inlineStr">
         <is>
           <t>web</t>
@@ -9878,7 +10188,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB69" t="inlineStr"/>
+      <c r="BB69" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC69" t="inlineStr">
         <is>
           <t>web</t>
@@ -9960,9 +10274,9 @@
       <c r="R70" t="n">
         <v>0</v>
       </c>
-      <c r="AA70" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
@@ -9972,13 +10286,23 @@
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR70" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="n">
         <v>0</v>
       </c>
+      <c r="AU70" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV70" t="inlineStr">
         <is>
           <t>all</t>
@@ -9989,6 +10313,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY70" t="inlineStr">
         <is>
           <t>web</t>
@@ -10004,7 +10333,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB70" t="inlineStr"/>
+      <c r="BB70" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC70" t="inlineStr">
         <is>
           <t>web</t>
@@ -10086,9 +10419,9 @@
       <c r="R71" t="n">
         <v>0</v>
       </c>
-      <c r="AA71" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
@@ -10098,13 +10431,23 @@
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR71" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS71" t="inlineStr"/>
       <c r="AT71" t="n">
         <v>0</v>
       </c>
+      <c r="AU71" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV71" t="inlineStr">
         <is>
           <t>all</t>
@@ -10115,6 +10458,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY71" t="inlineStr">
         <is>
           <t>web</t>
@@ -10130,7 +10478,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB71" t="inlineStr"/>
+      <c r="BB71" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC71" t="inlineStr">
         <is>
           <t>web</t>
@@ -10212,9 +10564,9 @@
       <c r="R72" t="n">
         <v>0</v>
       </c>
-      <c r="AA72" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
@@ -10224,13 +10576,23 @@
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR72" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="n">
         <v>0</v>
       </c>
+      <c r="AU72" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV72" t="inlineStr">
         <is>
           <t>all</t>
@@ -10241,6 +10603,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY72" t="inlineStr">
         <is>
           <t>web</t>
@@ -10256,7 +10623,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB72" t="inlineStr"/>
+      <c r="BB72" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC72" t="inlineStr">
         <is>
           <t>web</t>
@@ -10338,9 +10709,9 @@
       <c r="R73" t="n">
         <v>0</v>
       </c>
-      <c r="AA73" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
@@ -10350,13 +10721,23 @@
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR73" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS73" t="inlineStr"/>
       <c r="AT73" t="n">
         <v>0</v>
       </c>
+      <c r="AU73" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV73" t="inlineStr">
         <is>
           <t>all</t>
@@ -10367,6 +10748,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY73" t="inlineStr">
         <is>
           <t>web</t>
@@ -10382,7 +10768,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB73" t="inlineStr"/>
+      <c r="BB73" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC73" t="inlineStr">
         <is>
           <t>web</t>
@@ -10464,9 +10854,9 @@
       <c r="R74" t="n">
         <v>0</v>
       </c>
-      <c r="AA74" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
@@ -10476,13 +10866,23 @@
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR74" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="n">
         <v>0</v>
       </c>
+      <c r="AU74" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV74" t="inlineStr">
         <is>
           <t>all</t>
@@ -10493,6 +10893,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY74" t="inlineStr">
         <is>
           <t>web</t>
@@ -10508,7 +10913,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB74" t="inlineStr"/>
+      <c r="BB74" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC74" t="inlineStr">
         <is>
           <t>web</t>
@@ -10590,9 +10999,9 @@
       <c r="R75" t="n">
         <v>0</v>
       </c>
-      <c r="AA75" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
@@ -10602,13 +11011,23 @@
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR75" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="n">
         <v>0</v>
       </c>
+      <c r="AU75" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV75" t="inlineStr">
         <is>
           <t>all</t>
@@ -10619,6 +11038,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY75" t="inlineStr">
         <is>
           <t>web</t>
@@ -10634,7 +11058,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB75" t="inlineStr"/>
+      <c r="BB75" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC75" t="inlineStr">
         <is>
           <t>web</t>
@@ -10716,9 +11144,9 @@
       <c r="R76" t="n">
         <v>0</v>
       </c>
-      <c r="AA76" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
@@ -10728,13 +11156,23 @@
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR76" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS76" t="inlineStr"/>
       <c r="AT76" t="n">
         <v>0</v>
       </c>
+      <c r="AU76" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV76" t="inlineStr">
         <is>
           <t>all</t>
@@ -10745,6 +11183,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY76" t="inlineStr">
         <is>
           <t>web</t>
@@ -10760,7 +11203,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB76" t="inlineStr"/>
+      <c r="BB76" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC76" t="inlineStr">
         <is>
           <t>web</t>
@@ -10842,9 +11289,9 @@
       <c r="R77" t="n">
         <v>0</v>
       </c>
-      <c r="AA77" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
@@ -10854,13 +11301,23 @@
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR77" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS77" t="inlineStr"/>
       <c r="AT77" t="n">
         <v>0</v>
       </c>
+      <c r="AU77" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV77" t="inlineStr">
         <is>
           <t>all</t>
@@ -10871,6 +11328,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY77" t="inlineStr">
         <is>
           <t>web</t>
@@ -10886,7 +11348,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB77" t="inlineStr"/>
+      <c r="BB77" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC77" t="inlineStr">
         <is>
           <t>web</t>
@@ -10968,9 +11434,9 @@
       <c r="R78" t="n">
         <v>0</v>
       </c>
-      <c r="AA78" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
@@ -10980,13 +11446,23 @@
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR78" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="n">
         <v>0</v>
       </c>
+      <c r="AU78" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV78" t="inlineStr">
         <is>
           <t>all</t>
@@ -10997,6 +11473,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY78" t="inlineStr">
         <is>
           <t>web</t>
@@ -11012,7 +11493,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB78" t="inlineStr"/>
+      <c r="BB78" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC78" t="inlineStr">
         <is>
           <t>web</t>
@@ -11094,9 +11579,9 @@
       <c r="R79" t="n">
         <v>0</v>
       </c>
-      <c r="AA79" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
@@ -11106,13 +11591,23 @@
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR79" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS79" t="inlineStr"/>
       <c r="AT79" t="n">
         <v>0</v>
       </c>
+      <c r="AU79" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV79" t="inlineStr">
         <is>
           <t>all</t>
@@ -11123,6 +11618,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY79" t="inlineStr">
         <is>
           <t>web</t>
@@ -11138,7 +11638,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB79" t="inlineStr"/>
+      <c r="BB79" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC79" t="inlineStr">
         <is>
           <t>web</t>
@@ -11220,9 +11724,9 @@
       <c r="R80" t="n">
         <v>0</v>
       </c>
-      <c r="AA80" t="inlineStr">
-        <is>
-          <t>unknown</t>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
@@ -11232,13 +11736,23 @@
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR80" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS80" t="inlineStr"/>
       <c r="AT80" t="n">
         <v>0</v>
       </c>
+      <c r="AU80" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV80" t="inlineStr">
         <is>
           <t>all</t>
@@ -11249,6 +11763,11 @@
           <t>All Sources</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="AY80" t="inlineStr">
         <is>
           <t>web</t>
@@ -11264,7 +11783,11 @@
           <t>All Sources</t>
         </is>
       </c>
-      <c r="BB80" t="inlineStr"/>
+      <c r="BB80" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
       <c r="BC80" t="inlineStr">
         <is>
           <t>web</t>
